--- a/Config/Datas/drop.xlsx
+++ b/Config/Datas/drop.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="81">
   <si>
     <t>##var</t>
   </si>
@@ -107,6 +107,39 @@
     <t>破坏物（金箱子）</t>
   </si>
   <si>
+    <t>0档静态榨取</t>
+  </si>
+  <si>
+    <t>10000,10001</t>
+  </si>
+  <si>
+    <t>10000,10000</t>
+  </si>
+  <si>
+    <t>1档静态榨取</t>
+  </si>
+  <si>
+    <t>10010,10011,10012</t>
+  </si>
+  <si>
+    <t>10000,10000,1000</t>
+  </si>
+  <si>
+    <t>2档静态榨取</t>
+  </si>
+  <si>
+    <t>10020,10021,10022</t>
+  </si>
+  <si>
+    <t>随机欲望结晶</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>10000</t>
+  </si>
+  <si>
     <t>group_id</t>
   </si>
   <si>
@@ -159,6 +192,87 @@
   </si>
   <si>
     <t>10;15</t>
+  </si>
+  <si>
+    <t>少量欲望碎片</t>
+  </si>
+  <si>
+    <t>desire_shard</t>
+  </si>
+  <si>
+    <t>4;6</t>
+  </si>
+  <si>
+    <t>少量通识碎片</t>
+  </si>
+  <si>
+    <t>knowledge_shard</t>
+  </si>
+  <si>
+    <t>中量欲望碎片</t>
+  </si>
+  <si>
+    <t>12;17</t>
+  </si>
+  <si>
+    <t>中量通识碎片</t>
+  </si>
+  <si>
+    <t>中档 特殊奖励</t>
+  </si>
+  <si>
+    <t>5;8</t>
+  </si>
+  <si>
+    <t>大量欲望碎片</t>
+  </si>
+  <si>
+    <t>20;14</t>
+  </si>
+  <si>
+    <t>大量通识碎片</t>
+  </si>
+  <si>
+    <t>20;24</t>
+  </si>
+  <si>
+    <t>高档 特殊奖励1</t>
+  </si>
+  <si>
+    <t>random_desire_crystal</t>
+  </si>
+  <si>
+    <t>1;1</t>
+  </si>
+  <si>
+    <t>高档 特殊奖励2</t>
+  </si>
+  <si>
+    <t>40;40</t>
+  </si>
+  <si>
+    <t>随机欲望结晶1</t>
+  </si>
+  <si>
+    <t>desire_crystal_1</t>
+  </si>
+  <si>
+    <t>随机欲望结晶2</t>
+  </si>
+  <si>
+    <t>desire_crystal_2</t>
+  </si>
+  <si>
+    <t>随机欲望结晶3</t>
+  </si>
+  <si>
+    <t>desire_crystal_3</t>
+  </si>
+  <si>
+    <t>随机欲望结晶4</t>
+  </si>
+  <si>
+    <t>desire_crystal_4</t>
   </si>
 </sst>
 </file>
@@ -774,14 +888,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1095,12 +1212,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="5" max="5" width="28.25" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="5" max="5" width="28.25" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1116,10 +1233,10 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1136,10 +1253,10 @@
       <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1154,10 +1271,10 @@
       <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1174,10 +1291,10 @@
       <c r="D4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1191,10 +1308,10 @@
       <c r="D5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="2">
         <v>100</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2">
         <v>10000</v>
       </c>
     </row>
@@ -1208,10 +1325,10 @@
       <c r="D6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="2">
         <v>100</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2">
         <v>30000</v>
       </c>
     </row>
@@ -1225,10 +1342,10 @@
       <c r="D7" t="s">
         <v>22</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="2">
         <v>200</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2">
         <v>10000</v>
       </c>
     </row>
@@ -1242,10 +1359,10 @@
       <c r="D8" t="s">
         <v>23</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="2">
         <v>2000</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="2">
         <v>10000</v>
       </c>
     </row>
@@ -1259,11 +1376,76 @@
       <c r="D9" t="s">
         <v>24</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="2">
         <v>2001</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="2">
         <v>10000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="B11">
+        <v>1000</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="B12">
+        <v>1001</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="B13">
+        <v>1002</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="B15">
+        <v>99</v>
+      </c>
+      <c r="C15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1276,7 +1458,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="3" max="3" width="15" customWidth="1"/>
@@ -1298,16 +1480,16 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="G1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="H1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1330,7 +1512,7 @@
         <v>7</v>
       </c>
       <c r="G2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="H2" t="s">
         <v>9</v>
@@ -1374,24 +1556,24 @@
         <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="H4" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="B5" s="1">
-        <v>10001</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1">
@@ -1401,18 +1583,18 @@
         <v>100</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H5" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="B6" s="1">
-        <v>10002</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1">
@@ -1422,18 +1604,18 @@
         <v>100</v>
       </c>
       <c r="G6" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="H6" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="B7" s="1">
-        <v>20001</v>
+        <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1">
@@ -1443,18 +1625,18 @@
         <v>100</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H7" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="B8" s="1">
-        <v>20002</v>
+        <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1">
@@ -1464,18 +1646,18 @@
         <v>100</v>
       </c>
       <c r="G8" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="H8" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="B9">
-        <v>200001</v>
+      <c r="B9" s="1">
+        <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="E9">
         <v>2000</v>
@@ -1484,18 +1666,18 @@
         <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H9" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="B10">
-        <v>200002</v>
+      <c r="B10" s="1">
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="E10">
         <v>2000</v>
@@ -1504,18 +1686,18 @@
         <v>90</v>
       </c>
       <c r="G10" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H10" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="B11">
-        <v>200011</v>
+      <c r="B11" s="1">
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="E11">
         <v>2001</v>
@@ -1524,18 +1706,18 @@
         <v>90</v>
       </c>
       <c r="G11" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H11" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="B12">
-        <v>200012</v>
+      <c r="B12" s="1">
+        <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="E12">
         <v>2001</v>
@@ -1544,10 +1726,270 @@
         <v>10</v>
       </c>
       <c r="G12" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H12" t="s">
-        <v>42</v>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="B14">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14">
+        <v>10000</v>
+      </c>
+      <c r="F14">
+        <v>100</v>
+      </c>
+      <c r="G14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="B15">
+        <v>10</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15">
+        <v>10001</v>
+      </c>
+      <c r="F15">
+        <v>100</v>
+      </c>
+      <c r="G15" t="s">
+        <v>58</v>
+      </c>
+      <c r="H15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="B16">
+        <v>11</v>
+      </c>
+      <c r="C16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16">
+        <v>10010</v>
+      </c>
+      <c r="F16">
+        <v>100</v>
+      </c>
+      <c r="G16" t="s">
+        <v>55</v>
+      </c>
+      <c r="H16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17">
+        <v>10011</v>
+      </c>
+      <c r="F17">
+        <v>100</v>
+      </c>
+      <c r="G17" t="s">
+        <v>58</v>
+      </c>
+      <c r="H17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18">
+        <v>10012</v>
+      </c>
+      <c r="F18">
+        <v>100</v>
+      </c>
+      <c r="G18" t="s">
+        <v>46</v>
+      </c>
+      <c r="H18" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20">
+        <v>14</v>
+      </c>
+      <c r="C20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20">
+        <v>10020</v>
+      </c>
+      <c r="F20">
+        <v>100</v>
+      </c>
+      <c r="G20" t="s">
+        <v>55</v>
+      </c>
+      <c r="H20" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21">
+        <v>15</v>
+      </c>
+      <c r="C21" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21">
+        <v>10021</v>
+      </c>
+      <c r="F21">
+        <v>100</v>
+      </c>
+      <c r="G21" t="s">
+        <v>58</v>
+      </c>
+      <c r="H21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22">
+        <v>16</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22">
+        <v>10022</v>
+      </c>
+      <c r="F22">
+        <v>20</v>
+      </c>
+      <c r="G22" t="s">
+        <v>69</v>
+      </c>
+      <c r="H22" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23">
+        <v>17</v>
+      </c>
+      <c r="C23" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23">
+        <v>10022</v>
+      </c>
+      <c r="F23">
+        <v>80</v>
+      </c>
+      <c r="G23" t="s">
+        <v>46</v>
+      </c>
+      <c r="H23" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="B25">
+        <v>18</v>
+      </c>
+      <c r="C25" t="s">
+        <v>73</v>
+      </c>
+      <c r="E25">
+        <v>99</v>
+      </c>
+      <c r="F25">
+        <v>20</v>
+      </c>
+      <c r="G25" t="s">
+        <v>74</v>
+      </c>
+      <c r="H25" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="B26">
+        <v>19</v>
+      </c>
+      <c r="C26" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26">
+        <v>99</v>
+      </c>
+      <c r="F26">
+        <v>20</v>
+      </c>
+      <c r="G26" t="s">
+        <v>76</v>
+      </c>
+      <c r="H26" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8">
+      <c r="B27">
+        <v>20</v>
+      </c>
+      <c r="C27" t="s">
+        <v>77</v>
+      </c>
+      <c r="E27">
+        <v>99</v>
+      </c>
+      <c r="F27">
+        <v>20</v>
+      </c>
+      <c r="G27" t="s">
+        <v>78</v>
+      </c>
+      <c r="H27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28">
+        <v>21</v>
+      </c>
+      <c r="C28" t="s">
+        <v>79</v>
+      </c>
+      <c r="E28">
+        <v>99</v>
+      </c>
+      <c r="F28">
+        <v>20</v>
+      </c>
+      <c r="G28" t="s">
+        <v>80</v>
+      </c>
+      <c r="H28" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/drop.xlsx
+++ b/Config/Datas/drop.xlsx
@@ -110,25 +110,25 @@
     <t>0档静态榨取</t>
   </si>
   <si>
-    <t>10000,10001</t>
-  </si>
-  <si>
-    <t>10000,10000</t>
+    <t>10000;10001</t>
+  </si>
+  <si>
+    <t>10000;10000</t>
   </si>
   <si>
     <t>1档静态榨取</t>
   </si>
   <si>
-    <t>10010,10011,10012</t>
-  </si>
-  <si>
-    <t>10000,10000,1000</t>
+    <t>10010;10011;10012</t>
+  </si>
+  <si>
+    <t>10000;10000;1000</t>
   </si>
   <si>
     <t>2档静态榨取</t>
   </si>
   <si>
-    <t>10020,10021,10022</t>
+    <t>10020;10021;10022</t>
   </si>
   <si>
     <t>随机欲望结晶</t>

--- a/Config/Datas/drop.xlsx
+++ b/Config/Datas/drop.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="drop_bundle" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="88">
   <si>
     <t>##var</t>
   </si>
@@ -140,6 +140,12 @@
     <t>10000</t>
   </si>
   <si>
+    <t>牛逼箱子</t>
+  </si>
+  <si>
+    <t>999</t>
+  </si>
+  <si>
     <t>group_id</t>
   </si>
   <si>
@@ -273,6 +279,21 @@
   </si>
   <si>
     <t>desire_crystal_4</t>
+  </si>
+  <si>
+    <t>牛逼箱子1</t>
+  </si>
+  <si>
+    <t>牛逼箱子2</t>
+  </si>
+  <si>
+    <t>4;4</t>
+  </si>
+  <si>
+    <t>牛逼箱子3</t>
+  </si>
+  <si>
+    <t>40;60</t>
   </si>
 </sst>
 </file>
@@ -1212,7 +1233,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="22" customWidth="1"/>
@@ -1448,6 +1469,20 @@
         <v>35</v>
       </c>
     </row>
+    <row r="16" spans="1:6">
+      <c r="B16">
+        <v>999</v>
+      </c>
+      <c r="C16" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1458,7 +1493,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="3" max="3" width="15" customWidth="1"/>
@@ -1480,16 +1515,16 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1512,7 +1547,7 @@
         <v>7</v>
       </c>
       <c r="G2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H2" t="s">
         <v>9</v>
@@ -1556,16 +1591,16 @@
         <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1573,7 +1608,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1">
@@ -1583,10 +1618,10 @@
         <v>100</v>
       </c>
       <c r="G5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1594,7 +1629,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1">
@@ -1604,10 +1639,10 @@
         <v>100</v>
       </c>
       <c r="G6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1615,7 +1650,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1">
@@ -1625,10 +1660,10 @@
         <v>100</v>
       </c>
       <c r="G7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1636,7 +1671,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1">
@@ -1646,10 +1681,10 @@
         <v>100</v>
       </c>
       <c r="G8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1657,7 +1692,7 @@
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E9">
         <v>2000</v>
@@ -1666,10 +1701,10 @@
         <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1677,7 +1712,7 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E10">
         <v>2000</v>
@@ -1686,10 +1721,10 @@
         <v>90</v>
       </c>
       <c r="G10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1697,7 +1732,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E11">
         <v>2001</v>
@@ -1706,10 +1741,10 @@
         <v>90</v>
       </c>
       <c r="G11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1717,7 +1752,7 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E12">
         <v>2001</v>
@@ -1726,10 +1761,10 @@
         <v>10</v>
       </c>
       <c r="G12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1737,7 +1772,7 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E14">
         <v>10000</v>
@@ -1746,10 +1781,10 @@
         <v>100</v>
       </c>
       <c r="G14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1757,7 +1792,7 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E15">
         <v>10001</v>
@@ -1766,10 +1801,10 @@
         <v>100</v>
       </c>
       <c r="G15" t="s">
+        <v>60</v>
+      </c>
+      <c r="H15" t="s">
         <v>58</v>
-      </c>
-      <c r="H15" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1777,7 +1812,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E16">
         <v>10010</v>
@@ -1786,10 +1821,10 @@
         <v>100</v>
       </c>
       <c r="G16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="2:8">
@@ -1797,7 +1832,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E17">
         <v>10011</v>
@@ -1806,10 +1841,10 @@
         <v>100</v>
       </c>
       <c r="G17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H17" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="2:8">
@@ -1817,7 +1852,7 @@
         <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E18">
         <v>10012</v>
@@ -1826,10 +1861,10 @@
         <v>100</v>
       </c>
       <c r="G18" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H18" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="2:8">
@@ -1837,7 +1872,7 @@
         <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E20">
         <v>10020</v>
@@ -1846,10 +1881,10 @@
         <v>100</v>
       </c>
       <c r="G20" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H20" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="2:8">
@@ -1857,7 +1892,7 @@
         <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E21">
         <v>10021</v>
@@ -1866,10 +1901,10 @@
         <v>100</v>
       </c>
       <c r="G21" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H21" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="2:8">
@@ -1877,7 +1912,7 @@
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E22">
         <v>10022</v>
@@ -1886,10 +1921,10 @@
         <v>20</v>
       </c>
       <c r="G22" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H22" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="2:8">
@@ -1897,7 +1932,7 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E23">
         <v>10022</v>
@@ -1906,10 +1941,10 @@
         <v>80</v>
       </c>
       <c r="G23" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H23" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="2:8">
@@ -1917,7 +1952,7 @@
         <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E25">
         <v>99</v>
@@ -1926,10 +1961,10 @@
         <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H25" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="2:8">
@@ -1937,7 +1972,7 @@
         <v>19</v>
       </c>
       <c r="C26" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E26">
         <v>99</v>
@@ -1946,10 +1981,10 @@
         <v>20</v>
       </c>
       <c r="G26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H26" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="2:8">
@@ -1957,7 +1992,7 @@
         <v>20</v>
       </c>
       <c r="C27" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E27">
         <v>99</v>
@@ -1966,10 +2001,10 @@
         <v>20</v>
       </c>
       <c r="G27" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="2:8">
@@ -1977,7 +2012,7 @@
         <v>21</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E28">
         <v>99</v>
@@ -1986,10 +2021,70 @@
         <v>20</v>
       </c>
       <c r="G28" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H28" t="s">
-        <v>70</v>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="B30">
+        <v>22</v>
+      </c>
+      <c r="C30" t="s">
+        <v>83</v>
+      </c>
+      <c r="E30">
+        <v>999</v>
+      </c>
+      <c r="F30">
+        <v>20</v>
+      </c>
+      <c r="G30" t="s">
+        <v>48</v>
+      </c>
+      <c r="H30" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8">
+      <c r="B31">
+        <v>23</v>
+      </c>
+      <c r="C31" t="s">
+        <v>84</v>
+      </c>
+      <c r="E31">
+        <v>999</v>
+      </c>
+      <c r="F31">
+        <v>20</v>
+      </c>
+      <c r="G31" t="s">
+        <v>51</v>
+      </c>
+      <c r="H31" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8">
+      <c r="B32">
+        <v>24</v>
+      </c>
+      <c r="C32" t="s">
+        <v>86</v>
+      </c>
+      <c r="E32">
+        <v>999</v>
+      </c>
+      <c r="F32">
+        <v>60</v>
+      </c>
+      <c r="G32" t="s">
+        <v>57</v>
+      </c>
+      <c r="H32" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/drop.xlsx
+++ b/Config/Datas/drop.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="drop_bundle" sheetId="1" r:id="rId1"/>

--- a/Config/Datas/drop.xlsx
+++ b/Config/Datas/drop.xlsx
@@ -1011,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="22" customWidth="1" style="4" min="3" max="3"/>
@@ -1368,34 +1368,97 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="n">
+      <c r="B17" s="1" t="n">
         <v>900</v>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>家园草药采集</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="1" t="n">
         <v>9000</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="1" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="n">
+      <c r="B18" s="1" t="n">
         <v>901</v>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>家园木材采集</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="1" t="n">
         <v>9001</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="1" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="1" t="n">
+        <v>920</v>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>森林草丛搜刮</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>森林草丛搜刮</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>9200</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="1" t="n">
+        <v>921</v>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>森林灌木搜刮</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>森林灌木搜刮</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>9201</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="1" t="n">
+        <v>922</v>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>森林落叶堆搜刮</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>森林落叶堆搜刮</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>9202</v>
+      </c>
+      <c r="F21" s="1" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -1411,7 +1474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="15" customWidth="1" style="4" min="3" max="3"/>
@@ -2216,54 +2279,210 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="n">
+      <c r="B33" s="1" t="n">
         <v>9001</v>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>家园草药</t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="1" t="n">
         <v>9000</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="1" t="inlineStr">
         <is>
           <t>quest_mat_herb</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="1" t="inlineStr">
         <is>
           <t>1;1</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="n">
+      <c r="B34" s="1" t="n">
         <v>9002</v>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>家园木材</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="1" t="n">
         <v>9001</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="1" t="inlineStr">
         <is>
           <t>quest_mat_wood</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="1" t="inlineStr">
         <is>
           <t>1;1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="1" t="n">
+        <v>9201</v>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>草丛野果</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>9200</v>
+      </c>
+      <c r="F35" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>berry</t>
+        </is>
+      </c>
+      <c r="H35" s="1" t="inlineStr">
+        <is>
+          <t>1;2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="1" t="n">
+        <v>9202</v>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>草丛草药</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>9200</v>
+      </c>
+      <c r="F36" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="G36" s="1" t="inlineStr">
+        <is>
+          <t>quest_mat_herb</t>
+        </is>
+      </c>
+      <c r="H36" s="1" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="1" t="n">
+        <v>9211</v>
+      </c>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>灌木野果</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>9201</v>
+      </c>
+      <c r="F37" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="G37" s="1" t="inlineStr">
+        <is>
+          <t>berry</t>
+        </is>
+      </c>
+      <c r="H37" s="1" t="inlineStr">
+        <is>
+          <t>1;3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="1" t="n">
+        <v>9212</v>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>灌木木材</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>9201</v>
+      </c>
+      <c r="F38" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="G38" s="1" t="inlineStr">
+        <is>
+          <t>quest_mat_wood</t>
+        </is>
+      </c>
+      <c r="H38" s="1" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="1" t="n">
+        <v>9221</v>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>落叶堆小石子</t>
+        </is>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>9202</v>
+      </c>
+      <c r="F39" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="G39" s="1" t="inlineStr">
+        <is>
+          <t>small_stone</t>
+        </is>
+      </c>
+      <c r="H39" s="1" t="inlineStr">
+        <is>
+          <t>1;2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="1" t="n">
+        <v>9222</v>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>落叶堆零钱</t>
+        </is>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>9202</v>
+      </c>
+      <c r="F40" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="G40" s="1" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="H40" s="1" t="inlineStr">
+        <is>
+          <t>5;12</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/drop.xlsx
+++ b/Config/Datas/drop.xlsx
@@ -3,21 +3,21 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="drop_bundle" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="drop_item" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="2">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -27,344 +27,20 @@
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -372,258 +48,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -635,56 +66,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1002,6 +385,7 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -1011,133 +395,132 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="22" customWidth="1" style="4" min="3" max="3"/>
-    <col width="28.25" customWidth="1" style="2" min="5" max="5"/>
-    <col width="13" customWidth="1" style="2" min="6" max="6"/>
+    <col width="22" customWidth="1" style="3" min="3" max="3"/>
+    <col width="28.25" customWidth="1" style="1" min="5" max="5"/>
+    <col width="13" customWidth="1" style="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
         <is>
           <t>#desc</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>drop_group_ids</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>drop_group_weights</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>(list#sep=;),int</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>(list#sep=;),int</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n"/>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="67.5" customHeight="1" s="4">
-      <c r="A4" s="1" t="inlineStr">
+    <row r="4" ht="67.5" customHeight="1" s="3">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>掉落组列表</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>掉落组权重
 超过10000的部分必掉
@@ -1146,181 +529,181 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>城市杂物箱</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>描述1</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="1" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>城市杂物箱（大）</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>描述2</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="1" t="n">
         <v>30000</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>挖掘点（小）</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>挖掘点（小）</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="1" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>破坏物（灰箱子）</t>
         </is>
       </c>
-      <c r="D8" s="1" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>破坏物（灰箱子）</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="1" t="n">
         <v>2000</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="1" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="0" t="n">
         <v>201</v>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>破坏物（金箱子）</t>
         </is>
       </c>
-      <c r="D9" s="1" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>破坏物（金箱子）</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="1" t="n">
         <v>2001</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="1" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="0" t="n">
         <v>1000</v>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>0档静态榨取</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>0档静态榨取</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="1" t="inlineStr">
         <is>
           <t>10000;10001</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="1" t="inlineStr">
         <is>
           <t>10000;10000</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="0" t="n">
         <v>1001</v>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>1档静态榨取</t>
         </is>
       </c>
-      <c r="D12" s="1" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>1档静态榨取</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="1" t="inlineStr">
         <is>
           <t>10010;10011;10012</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="1" t="inlineStr">
         <is>
           <t>10000;10000;1000</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="0" t="n">
         <v>1002</v>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>2档静态榨取</t>
         </is>
       </c>
-      <c r="D13" s="1" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>2档静态榨取</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="1" t="inlineStr">
         <is>
           <t>10020;10021;10022</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="1" t="inlineStr">
         <is>
           <t>10000;10000;1000</t>
         </is>
@@ -1328,137 +711,168 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="0" t="n">
         <v>99</v>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C15" s="0" t="inlineStr">
         <is>
           <t>随机欲望结晶</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="1" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="1" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="0" t="n">
         <v>999</v>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>牛逼箱子</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="1" t="inlineStr">
         <is>
           <t>999</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="1" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="0" t="n">
         <v>900</v>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
         <is>
           <t>家园草药采集</t>
         </is>
       </c>
-      <c r="E17" s="1" t="n">
+      <c r="E17" s="0" t="n">
         <v>9000</v>
       </c>
-      <c r="F17" s="1" t="n">
+      <c r="F17" s="0" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="0" t="n">
         <v>901</v>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr">
         <is>
           <t>家园木材采集</t>
         </is>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="E18" s="0" t="n">
         <v>9001</v>
       </c>
-      <c r="F18" s="1" t="n">
+      <c r="F18" s="0" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="0" t="n">
         <v>920</v>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
         <is>
           <t>森林草丛搜刮</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="0" t="inlineStr">
         <is>
           <t>森林草丛搜刮</t>
         </is>
       </c>
-      <c r="E19" s="1" t="n">
+      <c r="E19" s="0" t="n">
         <v>9200</v>
       </c>
-      <c r="F19" s="1" t="n">
+      <c r="F19" s="0" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="0" t="n">
         <v>921</v>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C20" s="0" t="inlineStr">
         <is>
           <t>森林灌木搜刮</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="0" t="inlineStr">
         <is>
           <t>森林灌木搜刮</t>
         </is>
       </c>
-      <c r="E20" s="1" t="n">
+      <c r="E20" s="0" t="n">
         <v>9201</v>
       </c>
-      <c r="F20" s="1" t="n">
+      <c r="F20" s="0" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="0" t="n">
         <v>922</v>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr">
         <is>
           <t>森林落叶堆搜刮</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="0" t="inlineStr">
         <is>
           <t>森林落叶堆搜刮</t>
         </is>
       </c>
-      <c r="E21" s="1" t="n">
+      <c r="E21" s="0" t="n">
         <v>9202</v>
       </c>
-      <c r="F21" s="1" t="n">
+      <c r="F21" s="0" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" s="0" t="n"/>
+      <c r="E22" s="0" t="n"/>
+      <c r="F22" s="0" t="n"/>
+    </row>
+    <row r="23" s="3">
+      <c r="C23" s="0" t="n"/>
+      <c r="E23" s="0" t="n"/>
+      <c r="F23" s="0" t="n"/>
+    </row>
+    <row r="24" s="3">
+      <c r="B24" s="0" t="n">
+        <v>923</v>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>森林花露采集</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="inlineStr">
+        <is>
+          <t>森林北路普通花露采集点</t>
+        </is>
+      </c>
+      <c r="E24" s="0" t="n">
+        <v>9203</v>
+      </c>
+      <c r="F24" s="0" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -1474,385 +888,380 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="15" customWidth="1" style="4" min="3" max="3"/>
-    <col width="10.5" customWidth="1" style="4" min="5" max="6"/>
-    <col width="18" customWidth="1" style="4" min="7" max="8"/>
+    <col width="15" customWidth="1" style="3" min="3" max="3"/>
+    <col width="10.5" customWidth="1" style="3" min="5" max="6"/>
+    <col width="18" customWidth="1" style="3" min="7" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
         <is>
           <t>#desc</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>group_id</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>weight_in_group</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="0" t="inlineStr">
         <is>
           <t>item_id_list</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="0" t="inlineStr">
         <is>
           <t>item_count_range_list</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" s="0" t="inlineStr">
         <is>
           <t>(list#sep=;),string</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" s="0" t="inlineStr">
         <is>
           <t>(list#sep=;),int</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n"/>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="H3" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>所属掉落组</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>组内权重</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="G4" s="0" t="inlineStr">
         <is>
           <t>道具列表</t>
         </is>
       </c>
-      <c r="H4" s="1" t="inlineStr">
+      <c r="H4" s="0" t="inlineStr">
         <is>
           <t>道具数量波动</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>城市杂物箱1</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n"/>
-      <c r="E5" s="1" t="n">
+      <c r="E5" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="F5" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="H5" s="1" t="inlineStr">
+      <c r="H5" s="0" t="inlineStr">
         <is>
           <t>100;150</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>城市杂物箱2</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n"/>
-      <c r="E6" s="1" t="n">
+      <c r="E6" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="F6" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="G6" s="0" t="inlineStr">
         <is>
           <t>wood_board</t>
         </is>
       </c>
-      <c r="H6" s="1" t="inlineStr">
+      <c r="H6" s="0" t="inlineStr">
         <is>
           <t>2;5</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>城市杂物箱1</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n"/>
-      <c r="E7" s="1" t="n">
+      <c r="E7" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="F7" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="G7" s="0" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="H7" s="1" t="inlineStr">
+      <c r="H7" s="0" t="inlineStr">
         <is>
           <t>100;150</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>城市杂物箱2</t>
         </is>
       </c>
-      <c r="D8" s="1" t="n"/>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="F8" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="G8" s="0" t="inlineStr">
         <is>
           <t>wood_board</t>
         </is>
       </c>
-      <c r="H8" s="1" t="inlineStr">
+      <c r="H8" s="0" t="inlineStr">
         <is>
           <t>2;5</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>破坏灰箱</t>
         </is>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="E9" s="0" t="n">
         <v>2000</v>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="F9" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="G9" s="0" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="H9" s="1" t="inlineStr">
+      <c r="H9" s="0" t="inlineStr">
         <is>
           <t>50;65</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>破坏灰箱</t>
         </is>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="E10" s="0" t="n">
         <v>2000</v>
       </c>
-      <c r="F10" s="1" t="n">
+      <c r="F10" s="0" t="n">
         <v>90</v>
       </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="G10" s="0" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="H10" s="1" t="inlineStr">
+      <c r="H10" s="0" t="inlineStr">
         <is>
           <t>10;15</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>破坏灰箱</t>
         </is>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="E11" s="0" t="n">
         <v>2001</v>
       </c>
-      <c r="F11" s="1" t="n">
+      <c r="F11" s="0" t="n">
         <v>90</v>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="G11" s="0" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="H11" s="1" t="inlineStr">
+      <c r="H11" s="0" t="inlineStr">
         <is>
           <t>50;65</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>破坏灰箱</t>
         </is>
       </c>
-      <c r="E12" s="1" t="n">
+      <c r="E12" s="0" t="n">
         <v>2001</v>
       </c>
-      <c r="F12" s="1" t="n">
+      <c r="F12" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="G12" s="1" t="inlineStr">
+      <c r="G12" s="0" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="H12" s="1" t="inlineStr">
+      <c r="H12" s="0" t="inlineStr">
         <is>
           <t>10;15</t>
         </is>
@@ -1860,130 +1269,130 @@
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>少量欲望碎片</t>
         </is>
       </c>
-      <c r="E14" s="1" t="n">
+      <c r="E14" s="0" t="n">
         <v>10000</v>
       </c>
-      <c r="F14" s="1" t="n">
+      <c r="F14" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="G14" s="1" t="inlineStr">
+      <c r="G14" s="0" t="inlineStr">
         <is>
           <t>desire_shard</t>
         </is>
       </c>
-      <c r="H14" s="1" t="inlineStr">
+      <c r="H14" s="0" t="inlineStr">
         <is>
           <t>4;6</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C15" s="0" t="inlineStr">
         <is>
           <t>少量通识碎片</t>
         </is>
       </c>
-      <c r="E15" s="1" t="n">
+      <c r="E15" s="0" t="n">
         <v>10001</v>
       </c>
-      <c r="F15" s="1" t="n">
+      <c r="F15" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="G15" s="1" t="inlineStr">
+      <c r="G15" s="0" t="inlineStr">
         <is>
           <t>knowledge_shard</t>
         </is>
       </c>
-      <c r="H15" s="1" t="inlineStr">
+      <c r="H15" s="0" t="inlineStr">
         <is>
           <t>4;6</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>中量欲望碎片</t>
         </is>
       </c>
-      <c r="E16" s="1" t="n">
+      <c r="E16" s="0" t="n">
         <v>10010</v>
       </c>
-      <c r="F16" s="1" t="n">
+      <c r="F16" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="G16" s="1" t="inlineStr">
+      <c r="G16" s="0" t="inlineStr">
         <is>
           <t>desire_shard</t>
         </is>
       </c>
-      <c r="H16" s="1" t="inlineStr">
+      <c r="H16" s="0" t="inlineStr">
         <is>
           <t>12;17</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
         <is>
           <t>中量通识碎片</t>
         </is>
       </c>
-      <c r="E17" s="1" t="n">
+      <c r="E17" s="0" t="n">
         <v>10011</v>
       </c>
-      <c r="F17" s="1" t="n">
+      <c r="F17" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="G17" s="1" t="inlineStr">
+      <c r="G17" s="0" t="inlineStr">
         <is>
           <t>knowledge_shard</t>
         </is>
       </c>
-      <c r="H17" s="1" t="inlineStr">
+      <c r="H17" s="0" t="inlineStr">
         <is>
           <t>12;17</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr">
         <is>
           <t>中档 特殊奖励</t>
         </is>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="E18" s="0" t="n">
         <v>10012</v>
       </c>
-      <c r="F18" s="1" t="n">
+      <c r="F18" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="G18" s="1" t="inlineStr">
+      <c r="G18" s="0" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="H18" s="1" t="inlineStr">
+      <c r="H18" s="0" t="inlineStr">
         <is>
           <t>5;8</t>
         </is>
@@ -1991,104 +1400,104 @@
     </row>
     <row r="19"/>
     <row r="20">
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C20" s="0" t="inlineStr">
         <is>
           <t>大量欲望碎片</t>
         </is>
       </c>
-      <c r="E20" s="1" t="n">
+      <c r="E20" s="0" t="n">
         <v>10020</v>
       </c>
-      <c r="F20" s="1" t="n">
+      <c r="F20" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="G20" s="1" t="inlineStr">
+      <c r="G20" s="0" t="inlineStr">
         <is>
           <t>desire_shard</t>
         </is>
       </c>
-      <c r="H20" s="1" t="inlineStr">
+      <c r="H20" s="0" t="inlineStr">
         <is>
           <t>20;14</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr">
         <is>
           <t>大量通识碎片</t>
         </is>
       </c>
-      <c r="E21" s="1" t="n">
+      <c r="E21" s="0" t="n">
         <v>10021</v>
       </c>
-      <c r="F21" s="1" t="n">
+      <c r="F21" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="G21" s="1" t="inlineStr">
+      <c r="G21" s="0" t="inlineStr">
         <is>
           <t>knowledge_shard</t>
         </is>
       </c>
-      <c r="H21" s="1" t="inlineStr">
+      <c r="H21" s="0" t="inlineStr">
         <is>
           <t>20;24</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t>高档 特殊奖励1</t>
         </is>
       </c>
-      <c r="E22" s="1" t="n">
+      <c r="E22" s="0" t="n">
         <v>10022</v>
       </c>
-      <c r="F22" s="1" t="n">
+      <c r="F22" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="G22" s="1" t="inlineStr">
+      <c r="G22" s="0" t="inlineStr">
         <is>
           <t>random_desire_crystal</t>
         </is>
       </c>
-      <c r="H22" s="1" t="inlineStr">
+      <c r="H22" s="0" t="inlineStr">
         <is>
           <t>1;1</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>高档 特殊奖励2</t>
         </is>
       </c>
-      <c r="E23" s="1" t="n">
+      <c r="E23" s="0" t="n">
         <v>10022</v>
       </c>
-      <c r="F23" s="1" t="n">
+      <c r="F23" s="0" t="n">
         <v>80</v>
       </c>
-      <c r="G23" s="1" t="inlineStr">
+      <c r="G23" s="0" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="H23" s="1" t="inlineStr">
+      <c r="H23" s="0" t="inlineStr">
         <is>
           <t>40;40</t>
         </is>
@@ -2096,104 +1505,104 @@
     </row>
     <row r="24"/>
     <row r="25">
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>随机欲望结晶1</t>
         </is>
       </c>
-      <c r="E25" s="1" t="n">
+      <c r="E25" s="0" t="n">
         <v>99</v>
       </c>
-      <c r="F25" s="1" t="n">
+      <c r="F25" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="G25" s="1" t="inlineStr">
+      <c r="G25" s="0" t="inlineStr">
         <is>
           <t>desire_crystal_1</t>
         </is>
       </c>
-      <c r="H25" s="1" t="inlineStr">
+      <c r="H25" s="0" t="inlineStr">
         <is>
           <t>1;1</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr">
         <is>
           <t>随机欲望结晶2</t>
         </is>
       </c>
-      <c r="E26" s="1" t="n">
+      <c r="E26" s="0" t="n">
         <v>99</v>
       </c>
-      <c r="F26" s="1" t="n">
+      <c r="F26" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="G26" s="1" t="inlineStr">
+      <c r="G26" s="0" t="inlineStr">
         <is>
           <t>desire_crystal_2</t>
         </is>
       </c>
-      <c r="H26" s="1" t="inlineStr">
+      <c r="H26" s="0" t="inlineStr">
         <is>
           <t>1;1</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr">
         <is>
           <t>随机欲望结晶3</t>
         </is>
       </c>
-      <c r="E27" s="1" t="n">
+      <c r="E27" s="0" t="n">
         <v>99</v>
       </c>
-      <c r="F27" s="1" t="n">
+      <c r="F27" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="G27" s="1" t="inlineStr">
+      <c r="G27" s="0" t="inlineStr">
         <is>
           <t>desire_crystal_3</t>
         </is>
       </c>
-      <c r="H27" s="1" t="inlineStr">
+      <c r="H27" s="0" t="inlineStr">
         <is>
           <t>1;1</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C28" s="0" t="inlineStr">
         <is>
           <t>随机欲望结晶4</t>
         </is>
       </c>
-      <c r="E28" s="1" t="n">
+      <c r="E28" s="0" t="n">
         <v>99</v>
       </c>
-      <c r="F28" s="1" t="n">
+      <c r="F28" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="G28" s="1" t="inlineStr">
+      <c r="G28" s="0" t="inlineStr">
         <is>
           <t>desire_crystal_4</t>
         </is>
       </c>
-      <c r="H28" s="1" t="inlineStr">
+      <c r="H28" s="0" t="inlineStr">
         <is>
           <t>1;1</t>
         </is>
@@ -2201,288 +1610,333 @@
     </row>
     <row r="29"/>
     <row r="30">
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="0" t="n">
         <v>22</v>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C30" s="0" t="inlineStr">
         <is>
           <t>牛逼箱子1</t>
         </is>
       </c>
-      <c r="E30" s="1" t="n">
+      <c r="E30" s="0" t="n">
         <v>999</v>
       </c>
-      <c r="F30" s="1" t="n">
+      <c r="F30" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="G30" s="1" t="inlineStr">
+      <c r="G30" s="0" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="H30" s="1" t="inlineStr">
+      <c r="H30" s="0" t="inlineStr">
         <is>
           <t>40;40</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="0" t="n">
         <v>23</v>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C31" s="0" t="inlineStr">
         <is>
           <t>牛逼箱子2</t>
         </is>
       </c>
-      <c r="E31" s="1" t="n">
+      <c r="E31" s="0" t="n">
         <v>999</v>
       </c>
-      <c r="F31" s="1" t="n">
+      <c r="F31" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="G31" s="1" t="inlineStr">
+      <c r="G31" s="0" t="inlineStr">
         <is>
           <t>wood_board</t>
         </is>
       </c>
-      <c r="H31" s="1" t="inlineStr">
+      <c r="H31" s="0" t="inlineStr">
         <is>
           <t>4;4</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="0" t="n">
         <v>24</v>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C32" s="0" t="inlineStr">
         <is>
           <t>牛逼箱子3</t>
         </is>
       </c>
-      <c r="E32" s="1" t="n">
+      <c r="E32" s="0" t="n">
         <v>999</v>
       </c>
-      <c r="F32" s="1" t="n">
+      <c r="F32" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="G32" s="1" t="inlineStr">
+      <c r="G32" s="0" t="inlineStr">
         <is>
           <t>desire_shard</t>
         </is>
       </c>
-      <c r="H32" s="1" t="inlineStr">
+      <c r="H32" s="0" t="inlineStr">
         <is>
           <t>40;60</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="0" t="n">
         <v>9001</v>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C33" s="0" t="inlineStr">
         <is>
           <t>家园草药</t>
         </is>
       </c>
-      <c r="E33" s="1" t="n">
+      <c r="E33" s="0" t="n">
         <v>9000</v>
       </c>
-      <c r="F33" s="1" t="n">
+      <c r="F33" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="G33" s="1" t="inlineStr">
+      <c r="G33" s="0" t="inlineStr">
         <is>
           <t>quest_mat_herb</t>
         </is>
       </c>
-      <c r="H33" s="1" t="inlineStr">
+      <c r="H33" s="0" t="inlineStr">
         <is>
           <t>1;1</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="0" t="n">
         <v>9002</v>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C34" s="0" t="inlineStr">
         <is>
           <t>家园木材</t>
         </is>
       </c>
-      <c r="E34" s="1" t="n">
+      <c r="E34" s="0" t="n">
         <v>9001</v>
       </c>
-      <c r="F34" s="1" t="n">
+      <c r="F34" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="G34" s="1" t="inlineStr">
+      <c r="G34" s="0" t="inlineStr">
         <is>
           <t>quest_mat_wood</t>
         </is>
       </c>
-      <c r="H34" s="1" t="inlineStr">
+      <c r="H34" s="0" t="inlineStr">
         <is>
           <t>1;1</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="0" t="n">
         <v>9201</v>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C35" s="0" t="inlineStr">
         <is>
           <t>草丛野果</t>
         </is>
       </c>
-      <c r="E35" s="1" t="n">
+      <c r="E35" s="0" t="n">
         <v>9200</v>
       </c>
-      <c r="F35" s="1" t="n">
+      <c r="F35" s="0" t="n">
         <v>70</v>
       </c>
-      <c r="G35" s="1" t="inlineStr">
+      <c r="G35" s="0" t="inlineStr">
         <is>
           <t>berry</t>
         </is>
       </c>
-      <c r="H35" s="1" t="inlineStr">
+      <c r="H35" s="0" t="inlineStr">
         <is>
           <t>1;2</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="0" t="n">
         <v>9202</v>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C36" s="0" t="inlineStr">
         <is>
           <t>草丛草药</t>
         </is>
       </c>
-      <c r="E36" s="1" t="n">
+      <c r="E36" s="0" t="n">
         <v>9200</v>
       </c>
-      <c r="F36" s="1" t="n">
+      <c r="F36" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="G36" s="1" t="inlineStr">
+      <c r="G36" s="0" t="inlineStr">
         <is>
           <t>quest_mat_herb</t>
         </is>
       </c>
-      <c r="H36" s="1" t="inlineStr">
+      <c r="H36" s="0" t="inlineStr">
         <is>
           <t>1;1</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="0" t="n">
         <v>9211</v>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C37" s="0" t="inlineStr">
         <is>
           <t>灌木野果</t>
         </is>
       </c>
-      <c r="E37" s="1" t="n">
+      <c r="E37" s="0" t="n">
         <v>9201</v>
       </c>
-      <c r="F37" s="1" t="n">
+      <c r="F37" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="G37" s="1" t="inlineStr">
+      <c r="G37" s="0" t="inlineStr">
         <is>
           <t>berry</t>
         </is>
       </c>
-      <c r="H37" s="1" t="inlineStr">
+      <c r="H37" s="0" t="inlineStr">
         <is>
           <t>1;3</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="0" t="n">
         <v>9212</v>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C38" s="0" t="inlineStr">
         <is>
           <t>灌木木材</t>
         </is>
       </c>
-      <c r="E38" s="1" t="n">
+      <c r="E38" s="0" t="n">
         <v>9201</v>
       </c>
-      <c r="F38" s="1" t="n">
+      <c r="F38" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="G38" s="1" t="inlineStr">
+      <c r="G38" s="0" t="inlineStr">
         <is>
           <t>quest_mat_wood</t>
         </is>
       </c>
-      <c r="H38" s="1" t="inlineStr">
+      <c r="H38" s="0" t="inlineStr">
         <is>
           <t>1;1</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="0" t="n">
         <v>9221</v>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C39" s="0" t="inlineStr">
         <is>
           <t>落叶堆小石子</t>
         </is>
       </c>
-      <c r="E39" s="1" t="n">
+      <c r="E39" s="0" t="n">
         <v>9202</v>
       </c>
-      <c r="F39" s="1" t="n">
+      <c r="F39" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="G39" s="1" t="inlineStr">
+      <c r="G39" s="0" t="inlineStr">
         <is>
           <t>small_stone</t>
         </is>
       </c>
-      <c r="H39" s="1" t="inlineStr">
+      <c r="H39" s="0" t="inlineStr">
         <is>
           <t>1;2</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="0" t="n">
         <v>9222</v>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C40" s="0" t="inlineStr">
         <is>
           <t>落叶堆零钱</t>
         </is>
       </c>
-      <c r="E40" s="1" t="n">
+      <c r="E40" s="0" t="n">
         <v>9202</v>
       </c>
-      <c r="F40" s="1" t="n">
+      <c r="F40" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="G40" s="1" t="inlineStr">
+      <c r="G40" s="0" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
       </c>
-      <c r="H40" s="1" t="inlineStr">
+      <c r="H40" s="0" t="inlineStr">
         <is>
           <t>5;12</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" s="0" t="n"/>
+      <c r="E41" s="0" t="n"/>
+      <c r="F41" s="0" t="n"/>
+      <c r="G41" s="0" t="n"/>
+      <c r="H41" s="0" t="n"/>
+    </row>
+    <row r="42" s="3">
+      <c r="C42" s="0" t="n"/>
+      <c r="E42" s="0" t="n"/>
+      <c r="F42" s="0" t="n"/>
+      <c r="G42" s="0" t="n"/>
+      <c r="H42" s="0" t="n"/>
+    </row>
+    <row r="43" s="3">
+      <c r="B43" s="0" t="n">
+        <v>9231</v>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t>森林花露</t>
+        </is>
+      </c>
+      <c r="D43" s="0" t="inlineStr">
+        <is>
+          <t>叶尖与花瓣上凝结的普通森林花露</t>
+        </is>
+      </c>
+      <c r="E43" s="0" t="n">
+        <v>9203</v>
+      </c>
+      <c r="F43" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="G43" s="0" t="inlineStr">
+        <is>
+          <t>mat_forest_dew</t>
+        </is>
+      </c>
+      <c r="H43" s="0" t="inlineStr">
+        <is>
+          <t>1;2</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/drop.xlsx
+++ b/Config/Datas/drop.xlsx
@@ -395,7 +395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="22" customWidth="1" style="3" min="3" max="3"/>
@@ -633,7 +633,6 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="B11" s="0" t="n">
         <v>1000</v>
@@ -709,7 +708,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="B15" s="0" t="n">
         <v>99</v>
@@ -874,6 +872,27 @@
       </c>
       <c r="F24" s="0" t="n">
         <v>10000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>Premium Essence Drop Bundle</t>
+        </is>
+      </c>
+      <c r="D25" s="0" t="inlineStr"/>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="F25" s="0" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -888,7 +907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="15" customWidth="1" style="3" min="3" max="3"/>
@@ -937,6 +956,21 @@
           <t>item_count_range_list</t>
         </is>
       </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_type</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>premium_concentration_min</t>
+        </is>
+      </c>
+      <c r="K1" s="0" t="inlineStr">
+        <is>
+          <t>premium_concentration_max</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -979,6 +1013,21 @@
           <t>(list#sep=;),int</t>
         </is>
       </c>
+      <c r="I2" s="0" t="inlineStr">
+        <is>
+          <t>demo.EJingYuanType</t>
+        </is>
+      </c>
+      <c r="J2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
@@ -1016,6 +1065,21 @@
           <t>c</t>
         </is>
       </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="J3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="K3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
@@ -1058,6 +1122,21 @@
           <t>道具数量波动</t>
         </is>
       </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t>????????</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+      <c r="K4" s="0" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="0" t="n">
@@ -1083,6 +1162,17 @@
         <is>
           <t>100;150</t>
         </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1110,6 +1200,17 @@
           <t>2;5</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="0" t="n">
@@ -1136,6 +1237,17 @@
           <t>100;150</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="0" t="n">
@@ -1162,6 +1274,17 @@
           <t>2;5</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="0" t="n">
@@ -1188,6 +1311,17 @@
           <t>50;65</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="0" t="n">
@@ -1214,6 +1348,17 @@
           <t>10;15</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="0" t="n">
@@ -1240,6 +1385,17 @@
           <t>50;65</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="0" t="n">
@@ -1266,8 +1422,31 @@
           <t>10;15</t>
         </is>
       </c>
-    </row>
-    <row r="13"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="14">
       <c r="B14" s="0" t="n">
         <v>9</v>
@@ -1293,6 +1472,17 @@
           <t>4;6</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="0" t="n">
@@ -1319,6 +1509,17 @@
           <t>4;6</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="0" t="n">
@@ -1345,6 +1546,17 @@
           <t>12;17</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="0" t="n">
@@ -1371,6 +1583,17 @@
           <t>12;17</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="0" t="n">
@@ -1397,8 +1620,31 @@
           <t>5;8</t>
         </is>
       </c>
-    </row>
-    <row r="19"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="20">
       <c r="B20" s="0" t="n">
         <v>14</v>
@@ -1424,6 +1670,17 @@
           <t>20;14</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="B21" s="0" t="n">
@@ -1450,6 +1707,17 @@
           <t>20;24</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="0" t="n">
@@ -1476,6 +1744,17 @@
           <t>1;1</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="B23" s="0" t="n">
@@ -1502,8 +1781,31 @@
           <t>40;40</t>
         </is>
       </c>
-    </row>
-    <row r="24"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="25">
       <c r="B25" s="0" t="n">
         <v>18</v>
@@ -1529,6 +1831,17 @@
           <t>1;1</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="0" t="n">
@@ -1555,6 +1868,17 @@
           <t>1;1</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="B27" s="0" t="n">
@@ -1581,6 +1905,17 @@
           <t>1;1</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="B28" s="0" t="n">
@@ -1607,8 +1942,31 @@
           <t>1;1</t>
         </is>
       </c>
-    </row>
-    <row r="29"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="30">
       <c r="B30" s="0" t="n">
         <v>22</v>
@@ -1634,6 +1992,17 @@
           <t>40;40</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="B31" s="0" t="n">
@@ -1660,6 +2029,17 @@
           <t>4;4</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="B32" s="0" t="n">
@@ -1686,6 +2066,17 @@
           <t>40;60</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="B33" s="0" t="n">
@@ -1712,6 +2103,17 @@
           <t>1;1</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="B34" s="0" t="n">
@@ -1738,6 +2140,17 @@
           <t>1;1</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="B35" s="0" t="n">
@@ -1764,6 +2177,17 @@
           <t>1;2</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="B36" s="0" t="n">
@@ -1790,6 +2214,17 @@
           <t>1;1</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="B37" s="0" t="n">
@@ -1816,6 +2251,17 @@
           <t>1;3</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="B38" s="0" t="n">
@@ -1842,6 +2288,17 @@
           <t>1;1</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="B39" s="0" t="n">
@@ -1868,6 +2325,17 @@
           <t>1;2</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="B40" s="0" t="n">
@@ -1893,6 +2361,17 @@
         <is>
           <t>5;12</t>
         </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1901,6 +2380,17 @@
       <c r="F41" s="0" t="n"/>
       <c r="G41" s="0" t="n"/>
       <c r="H41" s="0" t="n"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42" s="3">
       <c r="C42" s="0" t="n"/>
@@ -1908,6 +2398,17 @@
       <c r="F42" s="0" t="n"/>
       <c r="G42" s="0" t="n"/>
       <c r="H42" s="0" t="n"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43" s="3">
       <c r="B43" s="0" t="n">
@@ -1938,6 +2439,2237 @@
         <is>
           <t>1;2</t>
         </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="0" t="n">
+        <v>30001</v>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t>?????? OrcI L1</t>
+        </is>
+      </c>
+      <c r="E44" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F44" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_orci_l1</t>
+        </is>
+      </c>
+      <c r="H44" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I44" s="0" t="inlineStr">
+        <is>
+          <t>OrcI</t>
+        </is>
+      </c>
+      <c r="J44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="0" t="n">
+        <v>30002</v>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t>?????? OrcI L2</t>
+        </is>
+      </c>
+      <c r="E45" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F45" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_orci_l2</t>
+        </is>
+      </c>
+      <c r="H45" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I45" s="0" t="inlineStr">
+        <is>
+          <t>OrcI</t>
+        </is>
+      </c>
+      <c r="J45" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="0" t="n">
+        <v>30003</v>
+      </c>
+      <c r="C46" s="0" t="inlineStr">
+        <is>
+          <t>?????? OrcI L3</t>
+        </is>
+      </c>
+      <c r="E46" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F46" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_orci_l3</t>
+        </is>
+      </c>
+      <c r="H46" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I46" s="0" t="inlineStr">
+        <is>
+          <t>OrcI</t>
+        </is>
+      </c>
+      <c r="J46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="0" t="n">
+        <v>30004</v>
+      </c>
+      <c r="C47" s="0" t="inlineStr">
+        <is>
+          <t>?????? OrcI L4</t>
+        </is>
+      </c>
+      <c r="E47" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F47" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_orci_l4</t>
+        </is>
+      </c>
+      <c r="H47" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I47" s="0" t="inlineStr">
+        <is>
+          <t>OrcI</t>
+        </is>
+      </c>
+      <c r="J47" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="0" t="n">
+        <v>30005</v>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t>?????? OrcI L5</t>
+        </is>
+      </c>
+      <c r="E48" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F48" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_orci_l5</t>
+        </is>
+      </c>
+      <c r="H48" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I48" s="0" t="inlineStr">
+        <is>
+          <t>OrcI</t>
+        </is>
+      </c>
+      <c r="J48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="0" t="n">
+        <v>30006</v>
+      </c>
+      <c r="C49" s="0" t="inlineStr">
+        <is>
+          <t>?????? OrcII L1</t>
+        </is>
+      </c>
+      <c r="E49" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F49" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_orcii_l1</t>
+        </is>
+      </c>
+      <c r="H49" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I49" s="0" t="inlineStr">
+        <is>
+          <t>OrcII</t>
+        </is>
+      </c>
+      <c r="J49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="0" t="n">
+        <v>30007</v>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t>?????? OrcII L2</t>
+        </is>
+      </c>
+      <c r="E50" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F50" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_orcii_l2</t>
+        </is>
+      </c>
+      <c r="H50" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I50" s="0" t="inlineStr">
+        <is>
+          <t>OrcII</t>
+        </is>
+      </c>
+      <c r="J50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="0" t="n">
+        <v>30008</v>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t>?????? OrcII L3</t>
+        </is>
+      </c>
+      <c r="E51" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F51" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_orcii_l3</t>
+        </is>
+      </c>
+      <c r="H51" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I51" s="0" t="inlineStr">
+        <is>
+          <t>OrcII</t>
+        </is>
+      </c>
+      <c r="J51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="0" t="n">
+        <v>30009</v>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t>?????? OrcII L4</t>
+        </is>
+      </c>
+      <c r="E52" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F52" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_orcii_l4</t>
+        </is>
+      </c>
+      <c r="H52" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I52" s="0" t="inlineStr">
+        <is>
+          <t>OrcII</t>
+        </is>
+      </c>
+      <c r="J52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="0" t="n">
+        <v>30010</v>
+      </c>
+      <c r="C53" s="0" t="inlineStr">
+        <is>
+          <t>?????? OrcII L5</t>
+        </is>
+      </c>
+      <c r="E53" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F53" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_orcii_l5</t>
+        </is>
+      </c>
+      <c r="H53" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I53" s="0" t="inlineStr">
+        <is>
+          <t>OrcII</t>
+        </is>
+      </c>
+      <c r="J53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="0" t="n">
+        <v>30011</v>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanI L1</t>
+        </is>
+      </c>
+      <c r="E54" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F54" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humani_l1</t>
+        </is>
+      </c>
+      <c r="H54" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I54" s="0" t="inlineStr">
+        <is>
+          <t>HumanI</t>
+        </is>
+      </c>
+      <c r="J54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="0" t="n">
+        <v>30012</v>
+      </c>
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanI L2</t>
+        </is>
+      </c>
+      <c r="E55" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F55" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humani_l2</t>
+        </is>
+      </c>
+      <c r="H55" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I55" s="0" t="inlineStr">
+        <is>
+          <t>HumanI</t>
+        </is>
+      </c>
+      <c r="J55" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="0" t="n">
+        <v>30013</v>
+      </c>
+      <c r="C56" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanI L3</t>
+        </is>
+      </c>
+      <c r="E56" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F56" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humani_l3</t>
+        </is>
+      </c>
+      <c r="H56" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I56" s="0" t="inlineStr">
+        <is>
+          <t>HumanI</t>
+        </is>
+      </c>
+      <c r="J56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="0" t="n">
+        <v>30014</v>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanI L4</t>
+        </is>
+      </c>
+      <c r="E57" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F57" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humani_l4</t>
+        </is>
+      </c>
+      <c r="H57" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I57" s="0" t="inlineStr">
+        <is>
+          <t>HumanI</t>
+        </is>
+      </c>
+      <c r="J57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="0" t="n">
+        <v>30015</v>
+      </c>
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanI L5</t>
+        </is>
+      </c>
+      <c r="E58" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F58" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humani_l5</t>
+        </is>
+      </c>
+      <c r="H58" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I58" s="0" t="inlineStr">
+        <is>
+          <t>HumanI</t>
+        </is>
+      </c>
+      <c r="J58" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="0" t="n">
+        <v>30016</v>
+      </c>
+      <c r="C59" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanII L1</t>
+        </is>
+      </c>
+      <c r="E59" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F59" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humanii_l1</t>
+        </is>
+      </c>
+      <c r="H59" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I59" s="0" t="inlineStr">
+        <is>
+          <t>HumanII</t>
+        </is>
+      </c>
+      <c r="J59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="0" t="n">
+        <v>30017</v>
+      </c>
+      <c r="C60" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanII L2</t>
+        </is>
+      </c>
+      <c r="E60" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F60" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humanii_l2</t>
+        </is>
+      </c>
+      <c r="H60" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I60" s="0" t="inlineStr">
+        <is>
+          <t>HumanII</t>
+        </is>
+      </c>
+      <c r="J60" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="0" t="n">
+        <v>30018</v>
+      </c>
+      <c r="C61" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanII L3</t>
+        </is>
+      </c>
+      <c r="E61" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F61" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humanii_l3</t>
+        </is>
+      </c>
+      <c r="H61" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I61" s="0" t="inlineStr">
+        <is>
+          <t>HumanII</t>
+        </is>
+      </c>
+      <c r="J61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="0" t="n">
+        <v>30019</v>
+      </c>
+      <c r="C62" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanII L4</t>
+        </is>
+      </c>
+      <c r="E62" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F62" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humanii_l4</t>
+        </is>
+      </c>
+      <c r="H62" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I62" s="0" t="inlineStr">
+        <is>
+          <t>HumanII</t>
+        </is>
+      </c>
+      <c r="J62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="0" t="n">
+        <v>30020</v>
+      </c>
+      <c r="C63" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanII L5</t>
+        </is>
+      </c>
+      <c r="E63" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F63" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humanii_l5</t>
+        </is>
+      </c>
+      <c r="H63" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I63" s="0" t="inlineStr">
+        <is>
+          <t>HumanII</t>
+        </is>
+      </c>
+      <c r="J63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="0" t="n">
+        <v>30021</v>
+      </c>
+      <c r="C64" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanIII L1</t>
+        </is>
+      </c>
+      <c r="E64" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F64" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humaniii_l1</t>
+        </is>
+      </c>
+      <c r="H64" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I64" s="0" t="inlineStr">
+        <is>
+          <t>HumanIII</t>
+        </is>
+      </c>
+      <c r="J64" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="0" t="n">
+        <v>30022</v>
+      </c>
+      <c r="C65" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanIII L2</t>
+        </is>
+      </c>
+      <c r="E65" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F65" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humaniii_l2</t>
+        </is>
+      </c>
+      <c r="H65" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I65" s="0" t="inlineStr">
+        <is>
+          <t>HumanIII</t>
+        </is>
+      </c>
+      <c r="J65" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="0" t="n">
+        <v>30023</v>
+      </c>
+      <c r="C66" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanIII L3</t>
+        </is>
+      </c>
+      <c r="E66" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F66" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humaniii_l3</t>
+        </is>
+      </c>
+      <c r="H66" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I66" s="0" t="inlineStr">
+        <is>
+          <t>HumanIII</t>
+        </is>
+      </c>
+      <c r="J66" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="0" t="n">
+        <v>30024</v>
+      </c>
+      <c r="C67" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanIII L4</t>
+        </is>
+      </c>
+      <c r="E67" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F67" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humaniii_l4</t>
+        </is>
+      </c>
+      <c r="H67" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I67" s="0" t="inlineStr">
+        <is>
+          <t>HumanIII</t>
+        </is>
+      </c>
+      <c r="J67" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="0" t="n">
+        <v>30025</v>
+      </c>
+      <c r="C68" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanIII L5</t>
+        </is>
+      </c>
+      <c r="E68" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F68" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humaniii_l5</t>
+        </is>
+      </c>
+      <c r="H68" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I68" s="0" t="inlineStr">
+        <is>
+          <t>HumanIII</t>
+        </is>
+      </c>
+      <c r="J68" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="0" t="n">
+        <v>30026</v>
+      </c>
+      <c r="C69" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanIV L1</t>
+        </is>
+      </c>
+      <c r="E69" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F69" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humaniv_l1</t>
+        </is>
+      </c>
+      <c r="H69" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I69" s="0" t="inlineStr">
+        <is>
+          <t>HumanIV</t>
+        </is>
+      </c>
+      <c r="J69" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="0" t="n">
+        <v>30027</v>
+      </c>
+      <c r="C70" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanIV L2</t>
+        </is>
+      </c>
+      <c r="E70" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F70" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humaniv_l2</t>
+        </is>
+      </c>
+      <c r="H70" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I70" s="0" t="inlineStr">
+        <is>
+          <t>HumanIV</t>
+        </is>
+      </c>
+      <c r="J70" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="0" t="n">
+        <v>30028</v>
+      </c>
+      <c r="C71" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanIV L3</t>
+        </is>
+      </c>
+      <c r="E71" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F71" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humaniv_l3</t>
+        </is>
+      </c>
+      <c r="H71" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I71" s="0" t="inlineStr">
+        <is>
+          <t>HumanIV</t>
+        </is>
+      </c>
+      <c r="J71" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="0" t="n">
+        <v>30029</v>
+      </c>
+      <c r="C72" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanIV L4</t>
+        </is>
+      </c>
+      <c r="E72" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F72" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humaniv_l4</t>
+        </is>
+      </c>
+      <c r="H72" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I72" s="0" t="inlineStr">
+        <is>
+          <t>HumanIV</t>
+        </is>
+      </c>
+      <c r="J72" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="0" t="n">
+        <v>30030</v>
+      </c>
+      <c r="C73" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanIV L5</t>
+        </is>
+      </c>
+      <c r="E73" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F73" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humaniv_l5</t>
+        </is>
+      </c>
+      <c r="H73" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I73" s="0" t="inlineStr">
+        <is>
+          <t>HumanIV</t>
+        </is>
+      </c>
+      <c r="J73" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="0" t="n">
+        <v>30031</v>
+      </c>
+      <c r="C74" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanV L1</t>
+        </is>
+      </c>
+      <c r="E74" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F74" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humanv_l1</t>
+        </is>
+      </c>
+      <c r="H74" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I74" s="0" t="inlineStr">
+        <is>
+          <t>HumanV</t>
+        </is>
+      </c>
+      <c r="J74" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="0" t="n">
+        <v>30032</v>
+      </c>
+      <c r="C75" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanV L2</t>
+        </is>
+      </c>
+      <c r="E75" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F75" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humanv_l2</t>
+        </is>
+      </c>
+      <c r="H75" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I75" s="0" t="inlineStr">
+        <is>
+          <t>HumanV</t>
+        </is>
+      </c>
+      <c r="J75" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="0" t="n">
+        <v>30033</v>
+      </c>
+      <c r="C76" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanV L3</t>
+        </is>
+      </c>
+      <c r="E76" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F76" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humanv_l3</t>
+        </is>
+      </c>
+      <c r="H76" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I76" s="0" t="inlineStr">
+        <is>
+          <t>HumanV</t>
+        </is>
+      </c>
+      <c r="J76" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="0" t="n">
+        <v>30034</v>
+      </c>
+      <c r="C77" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanV L4</t>
+        </is>
+      </c>
+      <c r="E77" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F77" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humanv_l4</t>
+        </is>
+      </c>
+      <c r="H77" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I77" s="0" t="inlineStr">
+        <is>
+          <t>HumanV</t>
+        </is>
+      </c>
+      <c r="J77" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="0" t="n">
+        <v>30035</v>
+      </c>
+      <c r="C78" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanV L5</t>
+        </is>
+      </c>
+      <c r="E78" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F78" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humanv_l5</t>
+        </is>
+      </c>
+      <c r="H78" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I78" s="0" t="inlineStr">
+        <is>
+          <t>HumanV</t>
+        </is>
+      </c>
+      <c r="J78" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="0" t="n">
+        <v>30036</v>
+      </c>
+      <c r="C79" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanVI L1</t>
+        </is>
+      </c>
+      <c r="E79" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F79" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humanvi_l1</t>
+        </is>
+      </c>
+      <c r="H79" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I79" s="0" t="inlineStr">
+        <is>
+          <t>HumanVI</t>
+        </is>
+      </c>
+      <c r="J79" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="0" t="n">
+        <v>30037</v>
+      </c>
+      <c r="C80" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanVI L2</t>
+        </is>
+      </c>
+      <c r="E80" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F80" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humanvi_l2</t>
+        </is>
+      </c>
+      <c r="H80" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I80" s="0" t="inlineStr">
+        <is>
+          <t>HumanVI</t>
+        </is>
+      </c>
+      <c r="J80" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="0" t="n">
+        <v>30038</v>
+      </c>
+      <c r="C81" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanVI L3</t>
+        </is>
+      </c>
+      <c r="E81" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F81" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humanvi_l3</t>
+        </is>
+      </c>
+      <c r="H81" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I81" s="0" t="inlineStr">
+        <is>
+          <t>HumanVI</t>
+        </is>
+      </c>
+      <c r="J81" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="0" t="n">
+        <v>30039</v>
+      </c>
+      <c r="C82" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanVI L4</t>
+        </is>
+      </c>
+      <c r="E82" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F82" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humanvi_l4</t>
+        </is>
+      </c>
+      <c r="H82" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I82" s="0" t="inlineStr">
+        <is>
+          <t>HumanVI</t>
+        </is>
+      </c>
+      <c r="J82" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="0" t="n">
+        <v>30040</v>
+      </c>
+      <c r="C83" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanVI L5</t>
+        </is>
+      </c>
+      <c r="E83" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F83" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humanvi_l5</t>
+        </is>
+      </c>
+      <c r="H83" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I83" s="0" t="inlineStr">
+        <is>
+          <t>HumanVI</t>
+        </is>
+      </c>
+      <c r="J83" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="0" t="n">
+        <v>30041</v>
+      </c>
+      <c r="C84" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanVII L1</t>
+        </is>
+      </c>
+      <c r="E84" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F84" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humanvii_l1</t>
+        </is>
+      </c>
+      <c r="H84" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I84" s="0" t="inlineStr">
+        <is>
+          <t>HumanVII</t>
+        </is>
+      </c>
+      <c r="J84" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="0" t="n">
+        <v>30042</v>
+      </c>
+      <c r="C85" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanVII L2</t>
+        </is>
+      </c>
+      <c r="E85" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F85" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humanvii_l2</t>
+        </is>
+      </c>
+      <c r="H85" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I85" s="0" t="inlineStr">
+        <is>
+          <t>HumanVII</t>
+        </is>
+      </c>
+      <c r="J85" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="0" t="n">
+        <v>30043</v>
+      </c>
+      <c r="C86" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanVII L3</t>
+        </is>
+      </c>
+      <c r="E86" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F86" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humanvii_l3</t>
+        </is>
+      </c>
+      <c r="H86" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I86" s="0" t="inlineStr">
+        <is>
+          <t>HumanVII</t>
+        </is>
+      </c>
+      <c r="J86" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="0" t="n">
+        <v>30044</v>
+      </c>
+      <c r="C87" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanVII L4</t>
+        </is>
+      </c>
+      <c r="E87" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F87" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humanvii_l4</t>
+        </is>
+      </c>
+      <c r="H87" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I87" s="0" t="inlineStr">
+        <is>
+          <t>HumanVII</t>
+        </is>
+      </c>
+      <c r="J87" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="0" t="n">
+        <v>30045</v>
+      </c>
+      <c r="C88" s="0" t="inlineStr">
+        <is>
+          <t>?????? HumanVII L5</t>
+        </is>
+      </c>
+      <c r="E88" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F88" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_humanvii_l5</t>
+        </is>
+      </c>
+      <c r="H88" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I88" s="0" t="inlineStr">
+        <is>
+          <t>HumanVII</t>
+        </is>
+      </c>
+      <c r="J88" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="0" t="n">
+        <v>30046</v>
+      </c>
+      <c r="C89" s="0" t="inlineStr">
+        <is>
+          <t>?????? MonsterI L1</t>
+        </is>
+      </c>
+      <c r="E89" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F89" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_monsteri_l1</t>
+        </is>
+      </c>
+      <c r="H89" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I89" s="0" t="inlineStr">
+        <is>
+          <t>MonsterI</t>
+        </is>
+      </c>
+      <c r="J89" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="0" t="n">
+        <v>30047</v>
+      </c>
+      <c r="C90" s="0" t="inlineStr">
+        <is>
+          <t>?????? MonsterI L2</t>
+        </is>
+      </c>
+      <c r="E90" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F90" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_monsteri_l2</t>
+        </is>
+      </c>
+      <c r="H90" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I90" s="0" t="inlineStr">
+        <is>
+          <t>MonsterI</t>
+        </is>
+      </c>
+      <c r="J90" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="0" t="n">
+        <v>30048</v>
+      </c>
+      <c r="C91" s="0" t="inlineStr">
+        <is>
+          <t>?????? MonsterI L3</t>
+        </is>
+      </c>
+      <c r="E91" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F91" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_monsteri_l3</t>
+        </is>
+      </c>
+      <c r="H91" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I91" s="0" t="inlineStr">
+        <is>
+          <t>MonsterI</t>
+        </is>
+      </c>
+      <c r="J91" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="0" t="n">
+        <v>30049</v>
+      </c>
+      <c r="C92" s="0" t="inlineStr">
+        <is>
+          <t>?????? MonsterI L4</t>
+        </is>
+      </c>
+      <c r="E92" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F92" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_monsteri_l4</t>
+        </is>
+      </c>
+      <c r="H92" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I92" s="0" t="inlineStr">
+        <is>
+          <t>MonsterI</t>
+        </is>
+      </c>
+      <c r="J92" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="0" t="n">
+        <v>30050</v>
+      </c>
+      <c r="C93" s="0" t="inlineStr">
+        <is>
+          <t>?????? MonsterI L5</t>
+        </is>
+      </c>
+      <c r="E93" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F93" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_monsteri_l5</t>
+        </is>
+      </c>
+      <c r="H93" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I93" s="0" t="inlineStr">
+        <is>
+          <t>MonsterI</t>
+        </is>
+      </c>
+      <c r="J93" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="0" t="n">
+        <v>30051</v>
+      </c>
+      <c r="C94" s="0" t="inlineStr">
+        <is>
+          <t>?????? MonsterII L1</t>
+        </is>
+      </c>
+      <c r="E94" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F94" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_monsterii_l1</t>
+        </is>
+      </c>
+      <c r="H94" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I94" s="0" t="inlineStr">
+        <is>
+          <t>MonsterII</t>
+        </is>
+      </c>
+      <c r="J94" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="0" t="n">
+        <v>30052</v>
+      </c>
+      <c r="C95" s="0" t="inlineStr">
+        <is>
+          <t>?????? MonsterII L2</t>
+        </is>
+      </c>
+      <c r="E95" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F95" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_monsterii_l2</t>
+        </is>
+      </c>
+      <c r="H95" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I95" s="0" t="inlineStr">
+        <is>
+          <t>MonsterII</t>
+        </is>
+      </c>
+      <c r="J95" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="0" t="n">
+        <v>30053</v>
+      </c>
+      <c r="C96" s="0" t="inlineStr">
+        <is>
+          <t>?????? MonsterII L3</t>
+        </is>
+      </c>
+      <c r="E96" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F96" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_monsterii_l3</t>
+        </is>
+      </c>
+      <c r="H96" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I96" s="0" t="inlineStr">
+        <is>
+          <t>MonsterII</t>
+        </is>
+      </c>
+      <c r="J96" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="0" t="n">
+        <v>30054</v>
+      </c>
+      <c r="C97" s="0" t="inlineStr">
+        <is>
+          <t>?????? MonsterII L4</t>
+        </is>
+      </c>
+      <c r="E97" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F97" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_monsterii_l4</t>
+        </is>
+      </c>
+      <c r="H97" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I97" s="0" t="inlineStr">
+        <is>
+          <t>MonsterII</t>
+        </is>
+      </c>
+      <c r="J97" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="0" t="n">
+        <v>30055</v>
+      </c>
+      <c r="C98" s="0" t="inlineStr">
+        <is>
+          <t>?????? MonsterII L5</t>
+        </is>
+      </c>
+      <c r="E98" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F98" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_monsterii_l5</t>
+        </is>
+      </c>
+      <c r="H98" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I98" s="0" t="inlineStr">
+        <is>
+          <t>MonsterII</t>
+        </is>
+      </c>
+      <c r="J98" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" s="0" t="n">
+        <v>30056</v>
+      </c>
+      <c r="C99" s="0" t="inlineStr">
+        <is>
+          <t>?????? MonsterIII L1</t>
+        </is>
+      </c>
+      <c r="E99" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F99" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_monsteriii_l1</t>
+        </is>
+      </c>
+      <c r="H99" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I99" s="0" t="inlineStr">
+        <is>
+          <t>MonsterIII</t>
+        </is>
+      </c>
+      <c r="J99" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="0" t="n">
+        <v>30057</v>
+      </c>
+      <c r="C100" s="0" t="inlineStr">
+        <is>
+          <t>?????? MonsterIII L2</t>
+        </is>
+      </c>
+      <c r="E100" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F100" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_monsteriii_l2</t>
+        </is>
+      </c>
+      <c r="H100" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I100" s="0" t="inlineStr">
+        <is>
+          <t>MonsterIII</t>
+        </is>
+      </c>
+      <c r="J100" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="0" t="n">
+        <v>30058</v>
+      </c>
+      <c r="C101" s="0" t="inlineStr">
+        <is>
+          <t>?????? MonsterIII L3</t>
+        </is>
+      </c>
+      <c r="E101" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F101" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_monsteriii_l3</t>
+        </is>
+      </c>
+      <c r="H101" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I101" s="0" t="inlineStr">
+        <is>
+          <t>MonsterIII</t>
+        </is>
+      </c>
+      <c r="J101" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" s="0" t="n">
+        <v>30059</v>
+      </c>
+      <c r="C102" s="0" t="inlineStr">
+        <is>
+          <t>?????? MonsterIII L4</t>
+        </is>
+      </c>
+      <c r="E102" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F102" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_monsteriii_l4</t>
+        </is>
+      </c>
+      <c r="H102" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I102" s="0" t="inlineStr">
+        <is>
+          <t>MonsterIII</t>
+        </is>
+      </c>
+      <c r="J102" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="0" t="n">
+        <v>30060</v>
+      </c>
+      <c r="C103" s="0" t="inlineStr">
+        <is>
+          <t>?????? MonsterIII L5</t>
+        </is>
+      </c>
+      <c r="E103" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F103" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="0" t="inlineStr">
+        <is>
+          <t>premium_essence_monsteriii_l5</t>
+        </is>
+      </c>
+      <c r="H103" s="0" t="inlineStr">
+        <is>
+          <t>1;1</t>
+        </is>
+      </c>
+      <c r="I103" s="0" t="inlineStr">
+        <is>
+          <t>MonsterIII</t>
+        </is>
+      </c>
+      <c r="J103" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="0" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/drop.xlsx
+++ b/Config/Datas/drop.xlsx
@@ -1163,15 +1163,15 @@
           <t>100;150</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="J5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1200,15 +1200,15 @@
           <t>2;5</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
+      <c r="J6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1237,15 +1237,15 @@
           <t>100;150</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
+      <c r="J7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1274,15 +1274,15 @@
           <t>2;5</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="J8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1311,15 +1311,15 @@
           <t>50;65</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="J9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1348,15 +1348,15 @@
           <t>10;15</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="J10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1385,15 +1385,15 @@
           <t>50;65</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="J11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1422,30 +1422,22 @@
           <t>10;15</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
+      <c r="J12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
+      <c r="I13" s="0" t="n"/>
+      <c r="J13" s="0" t="n"/>
+      <c r="K13" s="0" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="0" t="n">
@@ -1472,15 +1464,15 @@
           <t>4;6</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
+      <c r="J14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1509,15 +1501,15 @@
           <t>4;6</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
+      <c r="J15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1546,15 +1538,15 @@
           <t>12;17</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="J16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1583,15 +1575,15 @@
           <t>12;17</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="J17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1620,30 +1612,22 @@
           <t>5;8</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="J18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
+      <c r="I19" s="0" t="n"/>
+      <c r="J19" s="0" t="n"/>
+      <c r="K19" s="0" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="0" t="n">
@@ -1670,15 +1654,15 @@
           <t>20;14</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="J20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1707,15 +1691,15 @@
           <t>20;24</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
+      <c r="J21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1744,15 +1728,15 @@
           <t>1;1</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
+      <c r="J22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1781,30 +1765,22 @@
           <t>40;40</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
+      <c r="J23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
+      <c r="I24" s="0" t="n"/>
+      <c r="J24" s="0" t="n"/>
+      <c r="K24" s="0" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="0" t="n">
@@ -1831,15 +1807,15 @@
           <t>1;1</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
+      <c r="J25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1868,15 +1844,15 @@
           <t>1;1</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
+      <c r="J26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1905,15 +1881,15 @@
           <t>1;1</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
+      <c r="J27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1942,30 +1918,22 @@
           <t>1;1</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
+      <c r="J28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
+      <c r="I29" s="0" t="n"/>
+      <c r="J29" s="0" t="n"/>
+      <c r="K29" s="0" t="n"/>
     </row>
     <row r="30">
       <c r="B30" s="0" t="n">
@@ -1992,15 +1960,15 @@
           <t>40;40</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
+      <c r="J30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2029,15 +1997,15 @@
           <t>4;4</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
+      <c r="J31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2066,15 +2034,15 @@
           <t>40;60</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
+      <c r="J32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2103,15 +2071,15 @@
           <t>1;1</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
+      <c r="J33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2140,15 +2108,15 @@
           <t>1;1</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
+      <c r="J34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2177,15 +2145,15 @@
           <t>1;2</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
+      <c r="J35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2214,15 +2182,15 @@
           <t>1;1</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
+      <c r="J36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2251,15 +2219,15 @@
           <t>1;3</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
+      <c r="J37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2288,15 +2256,15 @@
           <t>1;1</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I38" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
+      <c r="J38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2325,15 +2293,15 @@
           <t>1;2</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
+      <c r="J39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2362,15 +2330,15 @@
           <t>5;12</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I40" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
+      <c r="J40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2380,17 +2348,9 @@
       <c r="F41" s="0" t="n"/>
       <c r="G41" s="0" t="n"/>
       <c r="H41" s="0" t="n"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
+      <c r="I41" s="0" t="n"/>
+      <c r="J41" s="0" t="n"/>
+      <c r="K41" s="0" t="n"/>
     </row>
     <row r="42" s="3">
       <c r="C42" s="0" t="n"/>
@@ -2398,17 +2358,9 @@
       <c r="F42" s="0" t="n"/>
       <c r="G42" s="0" t="n"/>
       <c r="H42" s="0" t="n"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
+      <c r="I42" s="0" t="n"/>
+      <c r="J42" s="0" t="n"/>
+      <c r="K42" s="0" t="n"/>
     </row>
     <row r="43" s="3">
       <c r="B43" s="0" t="n">
@@ -2440,15 +2392,15 @@
           <t>1;2</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
+      <c r="J43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="0" t="n">
         <v>0</v>
       </c>
     </row>
